--- a/docs/StructureDefinition-MedicationRequestUnsignedVAOrder.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsignedVAOrder.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsignedVAOrder.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsignedVAOrder.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>MedicationRequestUnsigned VA Order</t>
+    <t>MedicationRequest: Unsigned VA Order</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsignedVAOrder.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsignedVAOrder.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsignedVAOrder.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsignedVAOrder.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsignedVAOrder.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsignedVAOrder.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsignedVAOrder.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsignedVAOrder.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsignedVAOrder.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsignedVAOrder.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsignedVAOrder.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsignedVAOrder.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsignedVAOrder.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsignedVAOrder.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsignedVAOrder.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsignedVAOrder.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsignedVAOrder.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsignedVAOrder.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsignedVAOrder.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsignedVAOrder.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsignedVAOrder.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsignedVAOrder.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsignedVAOrder.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsignedVAOrder.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsignedVAOrder.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsignedVAOrder.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsignedVAOrder.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsignedVAOrder.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,6 +237,9 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
@@ -250,9 +253,6 @@
   </si>
   <si>
     <t>Mapping: HL7 v2 Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
   </si>
   <si>
     <t>Prescription
@@ -494,6 +494,9 @@
     <t>This is a business identifier, not a resource identifier.</t>
   </si>
   <si>
+    <t>1225: source value from ORDER - ORDER # (#100-.01) case package like 'PS%' &amp; class 'I' &amp; [exclude supply]</t>
+  </si>
+  <si>
     <t>Request.identifier</t>
   </si>
   <si>
@@ -507,9 +510,6 @@
   </si>
   <si>
     <t>ORC-2-Placer Order Number / ORC-3-Filler Order Number</t>
-  </si>
-  <si>
-    <t>1225: source value from ORDER - ORDER # (#100-.01) case package like 'PS%' &amp; class 'I' &amp; [exclude supply]</t>
   </si>
   <si>
     <t>MedicationRequest.status</t>
@@ -2277,12 +2277,12 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="101.44921875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="128.41796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="101.44921875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="128.41796875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2515,16 +2515,16 @@
         <v>86</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL2" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="AL2" t="s" s="2">
+      <c r="AM2" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="AM2" t="s" s="2">
+      <c r="AN2" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="AN2" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO2" t="s" s="2">
         <v>82</v>
@@ -3119,10 +3119,10 @@
         <v>82</v>
       </c>
       <c r="AM7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN7" t="s" s="2">
         <v>126</v>
-      </c>
-      <c r="AN7" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>82</v>
@@ -3239,10 +3239,10 @@
         <v>82</v>
       </c>
       <c r="AM8" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN8" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN8" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>82</v>
@@ -3359,10 +3359,10 @@
         <v>82</v>
       </c>
       <c r="AM9" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN9" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN9" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>82</v>
@@ -3481,10 +3481,10 @@
         <v>82</v>
       </c>
       <c r="AM10" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN10" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN10" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>82</v>
@@ -3715,19 +3715,19 @@
         <v>103</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL12" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="AL12" t="s" s="2">
+      <c r="AM12" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="AM12" t="s" s="2">
+      <c r="AN12" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AN12" t="s" s="2">
+      <c r="AO12" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AO12" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP12" t="s" s="2">
         <v>82</v>
@@ -3835,16 +3835,16 @@
         <v>103</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL13" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="AL13" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AM13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN13" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>82</v>
@@ -3955,19 +3955,19 @@
         <v>103</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL14" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="AL14" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AM14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN14" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="AN14" t="s" s="2">
+      <c r="AO14" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>82</v>
@@ -4076,16 +4076,16 @@
         <v>82</v>
       </c>
       <c r="AL15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM15" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="AM15" t="s" s="2">
+      <c r="AN15" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AN15" t="s" s="2">
+      <c r="AO15" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>82</v>
@@ -4198,16 +4198,16 @@
         <v>82</v>
       </c>
       <c r="AL16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM16" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="AM16" t="s" s="2">
+      <c r="AN16" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AN16" t="s" s="2">
+      <c r="AO16" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>82</v>
@@ -4313,19 +4313,19 @@
         <v>103</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="AL17" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AM17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN17" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="AN17" t="s" s="2">
+      <c r="AO17" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>82</v>
@@ -4439,10 +4439,10 @@
         <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN18" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>82</v>
@@ -4557,10 +4557,10 @@
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>82</v>
@@ -4669,22 +4669,22 @@
         <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL20" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AL20" t="s" s="2">
+      <c r="AM20" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AO20" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AO20" t="s" s="2">
+      <c r="AP20" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="21" hidden="true">
@@ -4789,22 +4789,22 @@
         <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL21" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="AL21" t="s" s="2">
+      <c r="AM21" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="AN21" t="s" s="2">
+      <c r="AO21" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="AO21" t="s" s="2">
+      <c r="AP21" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="AP21" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="22" hidden="true">
@@ -4909,22 +4909,22 @@
         <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL22" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="AL22" t="s" s="2">
+      <c r="AM22" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AN22" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="AO22" t="s" s="2">
+      <c r="AP22" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="AP22" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="23" hidden="true">
@@ -5027,19 +5027,19 @@
         <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="AL23" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AM23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="AN23" t="s" s="2">
+      <c r="AO23" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>82</v>
@@ -5145,22 +5145,22 @@
         <v>103</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL24" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="AL24" t="s" s="2">
+      <c r="AM24" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="AN24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="AO24" t="s" s="2">
+      <c r="AP24" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="25" hidden="true">
@@ -5263,19 +5263,19 @@
         <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL25" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="AL25" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AM25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -5381,19 +5381,19 @@
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL26" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="AL26" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AM26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AN26" t="s" s="2">
+      <c r="AO26" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -5501,16 +5501,16 @@
         <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL27" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="AL27" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AM27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
@@ -5625,13 +5625,13 @@
         <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="AN28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>82</v>
@@ -5739,22 +5739,22 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL29" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="AL29" t="s" s="2">
+      <c r="AM29" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="AM29" t="s" s="2">
+      <c r="AN29" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="AN29" t="s" s="2">
+      <c r="AO29" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AO29" t="s" s="2">
+      <c r="AP29" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="30" hidden="true">
@@ -5859,19 +5859,19 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AM30" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>82</v>
@@ -5977,16 +5977,16 @@
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL31" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="AL31" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AM31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN31" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -6101,10 +6101,10 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -6213,16 +6213,16 @@
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL33" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="AL33" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AM33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -6333,16 +6333,16 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL34" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="AL34" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AM34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6459,10 +6459,10 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6571,16 +6571,16 @@
         <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL36" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="AL36" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AM36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6689,16 +6689,16 @@
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="AL37" t="s" s="2">
+      <c r="AM37" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AN37" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6809,16 +6809,16 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="AL38" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AM38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -6933,10 +6933,10 @@
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -7053,10 +7053,10 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -7175,10 +7175,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7295,16 +7295,16 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="AN42" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AO42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP42" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="AP42" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="43" hidden="true">
@@ -7415,16 +7415,16 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="AN43" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AO43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP43" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="44" hidden="true">
@@ -7537,16 +7537,16 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="AN44" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AO44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP44" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="45" hidden="true">
@@ -7655,16 +7655,16 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="AN45" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AO45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP45" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="46" hidden="true">
@@ -7777,10 +7777,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN46" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7897,16 +7897,16 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="AN47" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AO47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP47" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="48" hidden="true">
@@ -8019,16 +8019,16 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="AN48" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AO48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP48" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="49" hidden="true">
@@ -8139,16 +8139,16 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="AN49" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AO49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP49" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="50" hidden="true">
@@ -8261,16 +8261,16 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="AN50" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AO50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP50" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="51" hidden="true">
@@ -8385,10 +8385,10 @@
         <v>82</v>
       </c>
       <c r="AO51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP51" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="52" hidden="true">
@@ -8497,10 +8497,10 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8617,10 +8617,10 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN53" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8743,10 +8743,10 @@
         <v>82</v>
       </c>
       <c r="AO54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP54" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="AP54" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="55" hidden="true">
@@ -8859,16 +8859,16 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN55" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="AN55" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AO55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP55" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="56" hidden="true">
@@ -8981,16 +8981,16 @@
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="AN56" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AO56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP56" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="AP56" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="57" hidden="true">
@@ -9103,16 +9103,16 @@
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN57" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="AN57" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AO57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP57" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="AP57" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="58" hidden="true">
@@ -9225,10 +9225,10 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN58" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9345,10 +9345,10 @@
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9460,13 +9460,13 @@
         <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM60" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="AM60" t="s" s="2">
+      <c r="AN60" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9581,10 +9581,10 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9701,10 +9701,10 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9823,10 +9823,10 @@
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN63" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9943,10 +9943,10 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -10061,10 +10061,10 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10181,10 +10181,10 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10303,10 +10303,10 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10421,10 +10421,10 @@
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10539,10 +10539,10 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN69" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10657,10 +10657,10 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN70" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10776,13 +10776,13 @@
         <v>82</v>
       </c>
       <c r="AL71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM71" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="AM71" t="s" s="2">
+      <c r="AN71" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -10896,19 +10896,19 @@
         <v>82</v>
       </c>
       <c r="AL72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM72" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="AM72" t="s" s="2">
+      <c r="AN72" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="AN72" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AO72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP72" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="73" hidden="true">
@@ -11014,19 +11014,19 @@
         <v>82</v>
       </c>
       <c r="AL73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM73" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="AM73" t="s" s="2">
+      <c r="AN73" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="AN73" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AO73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP73" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="AP73" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="74" hidden="true">
@@ -11134,13 +11134,13 @@
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM74" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="AM74" t="s" s="2">
+      <c r="AN74" t="s" s="2">
         <v>561</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11255,13 +11255,13 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="AN75" t="s" s="2">
+      <c r="AO75" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>82</v>
@@ -11370,13 +11370,13 @@
         <v>82</v>
       </c>
       <c r="AL76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM76" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="AM76" t="s" s="2">
+      <c r="AN76" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11491,10 +11491,10 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN77" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11611,10 +11611,10 @@
         <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN78" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11733,10 +11733,10 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN79" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -11850,19 +11850,19 @@
         <v>82</v>
       </c>
       <c r="AL80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM80" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="AM80" t="s" s="2">
+      <c r="AN80" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="AN80" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AO80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP80" t="s" s="2">
         <v>582</v>
-      </c>
-      <c r="AP80" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="81" hidden="true">
@@ -11968,19 +11968,19 @@
         <v>82</v>
       </c>
       <c r="AL81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM81" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="AM81" t="s" s="2">
+      <c r="AN81" t="s" s="2">
         <v>589</v>
       </c>
-      <c r="AN81" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AO81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP81" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="AP81" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="82" hidden="true">
@@ -12083,16 +12083,16 @@
         <v>103</v>
       </c>
       <c r="AK82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL82" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="AL82" t="s" s="2">
+      <c r="AM82" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="AM82" t="s" s="2">
+      <c r="AN82" t="s" s="2">
         <v>596</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
@@ -12209,10 +12209,10 @@
         <v>82</v>
       </c>
       <c r="AM83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN83" t="s" s="2">
         <v>603</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12323,16 +12323,16 @@
         <v>103</v>
       </c>
       <c r="AK84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL84" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="AL84" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AM84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN84" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-MedicationRequestUnsignedVAOrder.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsignedVAOrder.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsignedVAOrder.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsignedVAOrder.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsignedVAOrder.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsignedVAOrder.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestUnsignedVAOrder.xlsx
+++ b/docs/StructureDefinition-MedicationRequestUnsignedVAOrder.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
